--- a/Dictionnaires des données de la vague1.xlsx
+++ b/Dictionnaires des données de la vague1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OPINION WAY PROJECT\PROJET 2026\Nos AO\AO Betclic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CBAB032-E81F-49BE-A6E3-CF600697FE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B84069-4AEE-41DD-B3C9-53497D13F8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{1F219D56-78BA-4D09-853B-7CB5A192F88B}"/>
   </bookViews>
